--- a/product_selector_out/STM32U3B5-3C5 - diff.xlsx
+++ b/product_selector_out/STM32U3B5-3C5 - diff.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Diff" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$147</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,7 +33,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -65,6 +65,11 @@
         <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -81,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -91,6 +96,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -456,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E72"/>
+  <dimension ref="A1:E147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -549,7 +555,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9">
@@ -559,7 +565,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -609,7 +615,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -619,7 +625,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
@@ -629,7 +635,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1298</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="18">
@@ -875,18 +881,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E27" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -898,25 +908,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E28" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STM32U3C5CI</t>
+          <t>STM32U3B5CI</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -926,7 +940,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -934,70 +948,70 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STM32U3C5CI</t>
+          <t>STM32U3B5CI</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>33||37</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STM32U3C5CI</t>
+          <t>STM32U3B5CI</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>10 (workbook and API agree)</t>
+          <t>33, 37</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STM32U3C5CI</t>
+          <t>STM32U3B5CI</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1007,7 +1021,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>33||37</t>
+          <t>33||37 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1015,63 +1029,55 @@
           <t>37</t>
         </is>
       </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STM32U3C5CI</t>
+          <t>STM32U3B5CI</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>33, 37</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STM32U3C5CI</t>
+          <t>STM32U3B5CI</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>33||37 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -1083,18 +1089,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E35" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -1106,117 +1116,137 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E36" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STM32U3B5ZI</t>
+          <t>STM32U3C5CI</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>10 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E37" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>STM32U3B5ZI</t>
+          <t>STM32U3C5CI</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>33||37</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E38" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STM32U3C5ZI</t>
+          <t>STM32U3C5CI</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>33, 37</t>
+        </is>
+      </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E39" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>STM32U3C5ZI</t>
+          <t>STM32U3C5CI</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>33||37 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E40" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>STM32U3C5QI</t>
+          <t>STM32U3C5CI</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1239,7 +1269,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>STM32U3C5QI</t>
+          <t>STM32U3C5CI</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1262,145 +1292,169 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>STM32U3B5WG</t>
+          <t>STM32U3B5ZI</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E43" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STM32U3B5WG</t>
+          <t>STM32U3B5ZI</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E44" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>STM32U3C5WI</t>
+          <t>STM32U3B5ZI</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>10 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E45" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>STM32U3C5WI</t>
+          <t>STM32U3B5ZI</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>111||114</t>
+        </is>
+      </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E46" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>STM32U3B5RI</t>
+          <t>STM32U3B5ZI</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>111, 114</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E47" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>STM32U3B5RI</t>
+          <t>STM32U3B5ZI</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>111||114 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E48" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STM32U3B5RG</t>
+          <t>STM32U3B5ZI</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1423,7 +1477,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STM32U3B5RG</t>
+          <t>STM32U3B5ZI</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1446,145 +1500,169 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>STM32U3C5RI</t>
+          <t>STM32U3C5ZI</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E51" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>STM32U3C5RI</t>
+          <t>STM32U3C5ZI</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E52" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>STM32U3B5VI</t>
+          <t>STM32U3C5ZI</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>10 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E53" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>STM32U3B5VI</t>
+          <t>STM32U3C5ZI</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>111||114</t>
+        </is>
+      </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E54" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>STM32U3C5VI</t>
+          <t>STM32U3C5ZI</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>111, 114</t>
+        </is>
+      </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E55" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>STM32U3C5VI</t>
+          <t>STM32U3C5ZI</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>111||114 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E56" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>STM32U3B5WI</t>
+          <t>STM32U3C5ZI</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1607,7 +1685,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>STM32U3B5WI</t>
+          <t>STM32U3C5ZI</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1630,145 +1708,169 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>STM32U3C5JI</t>
+          <t>STM32U3C5QI</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E59" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STM32U3C5JI</t>
+          <t>STM32U3C5QI</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E60" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>STM32U3B5QI</t>
+          <t>STM32U3C5QI</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>10 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E61" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>STM32U3B5QI</t>
+          <t>STM32U3C5QI</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>106||110</t>
+        </is>
+      </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E62" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STM32U3B5VG</t>
+          <t>STM32U3C5QI</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>106, 110</t>
+        </is>
+      </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E63" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>STM32U3B5VG</t>
+          <t>STM32U3C5QI</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>106||110 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E64" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>STM32U3B5JI</t>
+          <t>STM32U3C5QI</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1791,7 +1893,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>STM32U3B5JI</t>
+          <t>STM32U3C5QI</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1814,87 +1916,99 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STM32U3B5ZG</t>
+          <t>STM32U3B5WG</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E67" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>STM32U3B5ZG</t>
+          <t>STM32U3B5WG</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E68" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STM32U3B5QG</t>
+          <t>STM32U3B5WG</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>10 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E69" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>STM32U3B5QG</t>
+          <t>STM32U3B5WG</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
@@ -1906,18 +2020,18 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>STM32U3B5JG</t>
+          <t>STM32U3B5WG</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
@@ -1929,28 +2043,1945 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
+          <t>STM32U3C5WI</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>STM32U3C5WI</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>STM32U3C5WI</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>10 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E74" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>STM32U3C5WI</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E75" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>STM32U3C5WI</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E76" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>STM32U3B5RI</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>STM32U3B5RI</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>STM32U3B5RI</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>10 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>STM32U3B5RI</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>47||51</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>STM32U3B5RI</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>47, 51</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>STM32U3B5RI</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>47||51 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>STM32U3B5RI</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E83" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>STM32U3B5RI</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E84" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>STM32U3B5RG</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>STM32U3B5RG</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>STM32U3B5RG</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>10 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E87" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>STM32U3B5RG</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>47||51</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>STM32U3B5RG</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>47, 51</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>STM32U3B5RG</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>47||51 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E90" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>STM32U3B5RG</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E91" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>STM32U3B5RG</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E92" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>STM32U3C5RI</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>STM32U3C5RI</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>STM32U3C5RI</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>10 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E95" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>STM32U3C5RI</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>47||51</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>STM32U3C5RI</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>47, 51</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>STM32U3C5RI</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>47||51 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E98" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>STM32U3C5RI</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E99" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>STM32U3C5RI</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E100" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>STM32U3B5VI</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E101" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>STM32U3B5VI</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E102" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>STM32U3C5VI</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E103" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>STM32U3C5VI</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E104" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>STM32U3B5WI</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>STM32U3B5WI</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E106" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>STM32U3B5WI</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>10 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E107" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>STM32U3B5WI</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E108" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>STM32U3B5WI</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E109" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>STM32U3C5JI</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E110" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>STM32U3C5JI</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E111" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>STM32U3C5JI</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E112" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>STM32U3C5JI</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E113" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>STM32U3B5QI</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E114" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>STM32U3B5QI</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E115" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>STM32U3B5QI</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>10 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E116" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>STM32U3B5QI</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>106||110</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>STM32U3B5QI</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>106, 110</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="E118" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>STM32U3B5QI</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>106||110 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="E119" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>STM32U3B5QI</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E120" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>STM32U3B5QI</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E121" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>STM32U3B5VG</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr"/>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E122" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>STM32U3B5VG</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E123" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>STM32U3B5JI</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E124" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>STM32U3B5JI</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E125" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>STM32U3B5JI</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr"/>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E126" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>STM32U3B5JI</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E127" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>STM32U3B5ZG</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E128" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>STM32U3B5ZG</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E129" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>STM32U3B5ZG</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>10 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E130" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>STM32U3B5ZG</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>111||114</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="E131" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>STM32U3B5ZG</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>111, 114</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="E132" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>STM32U3B5ZG</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>111||114 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="E133" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>STM32U3B5ZG</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E134" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>STM32U3B5ZG</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E135" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>STM32U3B5QG</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E136" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>STM32U3B5QG</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E137" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>STM32U3B5QG</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>10 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E138" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>STM32U3B5QG</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>106||110</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="E139" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>STM32U3B5QG</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>106, 110</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="E140" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>STM32U3B5QG</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>106||110 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="E141" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>STM32U3B5QG</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E142" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>STM32U3B5QG</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E143" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
           <t>STM32U3B5JG</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E144" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>STM32U3B5JG</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E145" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>STM32U3B5JG</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E146" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>STM32U3B5JG</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
         <is>
           <t>Longevity Starting Date</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr"/>
-      <c r="D72" t="inlineStr">
+      <c r="C147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
         <is>
           <t>2026-03-03T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E72" s="6" t="inlineStr">
+      <c r="E147" s="6" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A18:E72"/>
+  <autoFilter ref="A18:E147"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/product_selector_out/STM32U3B5-3C5 - diff.xlsx
+++ b/product_selector_out/STM32U3B5-3C5 - diff.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Diff" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$147</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$126</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E147"/>
+  <dimension ref="A1:E126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1269</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="18">
@@ -754,22 +754,18 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>33||37</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -781,95 +777,99 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>33, 37</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>STM32U3B5CG</t>
+          <t>STM32U3B5CI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>33||37 (workbook and API agree)</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>STM32U3B5CG</t>
+          <t>STM32U3B5CI</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>STM32U3B5CG</t>
+          <t>STM32U3B5CI</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>10 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E26" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -881,22 +881,18 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -908,29 +904,25 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STM32U3B5CI</t>
+          <t>STM32U3C5CI</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -940,7 +932,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>10 (workbook and API agree)</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -948,108 +940,104 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STM32U3B5CI</t>
+          <t>STM32U3C5CI</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>33||37</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STM32U3B5CI</t>
+          <t>STM32U3C5CI</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>33, 37</t>
+          <t>10 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STM32U3B5CI</t>
+          <t>STM32U3C5CI</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>33||37 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STM32U3B5CI</t>
+          <t>STM32U3C5CI</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
@@ -1061,30 +1049,34 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STM32U3B5CI</t>
+          <t>STM32U3B5ZI</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E34" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STM32U3C5CI</t>
+          <t>STM32U3B5ZI</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1102,16 +1094,16 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STM32U3C5CI</t>
+          <t>STM32U3B5ZI</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1121,7 +1113,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1129,158 +1121,154 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STM32U3C5CI</t>
+          <t>STM32U3B5ZI</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>10 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E37" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>STM32U3C5CI</t>
+          <t>STM32U3B5ZI</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>33||37</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STM32U3C5CI</t>
+          <t>STM32U3C5ZI</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>33, 37</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>STM32U3C5CI</t>
+          <t>STM32U3C5ZI</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>33||37 (workbook and API agree)</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="E40" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>STM32U3C5CI</t>
+          <t>STM32U3C5ZI</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>10 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E41" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>STM32U3C5CI</t>
+          <t>STM32U3C5ZI</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
@@ -1292,34 +1280,30 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>STM32U3B5ZI</t>
+          <t>STM32U3C5ZI</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STM32U3B5ZI</t>
+          <t>STM32U3C5QI</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1337,16 +1321,16 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>STM32U3B5ZI</t>
+          <t>STM32U3C5QI</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1356,7 +1340,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>10 (workbook and API agree)</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1364,143 +1348,143 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E45" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>STM32U3B5ZI</t>
+          <t>STM32U3C5QI</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>111||114</t>
+          <t>10 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>STM32U3B5ZI</t>
+          <t>STM32U3C5QI</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>111, 114</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>STM32U3B5ZI</t>
+          <t>STM32U3C5QI</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>111||114 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="E48" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STM32U3B5ZI</t>
+          <t>STM32U3B5WG</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E49" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STM32U3B5ZI</t>
+          <t>STM32U3B5WG</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E50" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>STM32U3C5ZI</t>
+          <t>STM32U3B5WG</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1510,7 +1494,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1518,85 +1502,77 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E51" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>STM32U3C5ZI</t>
+          <t>STM32U3B5WG</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>STM32U3C5ZI</t>
+          <t>STM32U3B5WG</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>10 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E53" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>STM32U3C5ZI</t>
+          <t>STM32U3C5WI</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>111||114</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
@@ -1608,22 +1584,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>STM32U3C5ZI</t>
+          <t>STM32U3C5WI</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>111, 114</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
@@ -1635,22 +1611,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>STM32U3C5ZI</t>
+          <t>STM32U3C5WI</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>111||114 (workbook and API agree)</t>
+          <t>10 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -1662,149 +1638,149 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>STM32U3C5ZI</t>
+          <t>STM32U3C5WI</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E57" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>STM32U3C5ZI</t>
+          <t>STM32U3C5WI</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E58" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>STM32U3C5QI</t>
+          <t>STM32U3C5WI</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>97 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E59" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STM32U3C5QI</t>
+          <t>STM32U3C5WI</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>STM32U3C5QI</t>
+          <t>STM32U3C5WI</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>10 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E61" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>STM32U3C5QI</t>
+          <t>STM32U3B5RI</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>106||110</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
@@ -1816,22 +1792,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STM32U3C5QI</t>
+          <t>STM32U3B5RI</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>106, 110</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
@@ -1843,22 +1819,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>STM32U3C5QI</t>
+          <t>STM32U3B5RI</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>106||110 (workbook and API agree)</t>
+          <t>10 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -1870,7 +1846,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>STM32U3C5QI</t>
+          <t>STM32U3B5RI</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1893,7 +1869,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>STM32U3C5QI</t>
+          <t>STM32U3B5RI</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1916,7 +1892,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STM32U3B5WG</t>
+          <t>STM32U3B5RG</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1943,7 +1919,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>STM32U3B5WG</t>
+          <t>STM32U3B5RG</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1970,7 +1946,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STM32U3B5WG</t>
+          <t>STM32U3B5RG</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1997,7 +1973,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>STM32U3B5WG</t>
+          <t>STM32U3B5RG</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2020,7 +1996,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>STM32U3B5WG</t>
+          <t>STM32U3B5RG</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2043,7 +2019,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>STM32U3C5WI</t>
+          <t>STM32U3C5RI</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2070,7 +2046,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>STM32U3C5WI</t>
+          <t>STM32U3C5RI</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2097,7 +2073,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>STM32U3C5WI</t>
+          <t>STM32U3C5RI</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2124,7 +2100,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>STM32U3C5WI</t>
+          <t>STM32U3C5RI</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2147,7 +2123,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>STM32U3C5WI</t>
+          <t>STM32U3C5RI</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2170,519 +2146,503 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>STM32U3B5RI</t>
+          <t>STM32U3B5VI</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E77" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>STM32U3B5RI</t>
+          <t>STM32U3B5VI</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E78" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>STM32U3B5RI</t>
+          <t>STM32U3C5VI</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>10 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E79" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>STM32U3B5RI</t>
+          <t>STM32U3C5VI</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>47||51</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="E80" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E80" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>STM32U3B5RI</t>
+          <t>STM32U3B5WI</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>47, 51</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="E81" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>STM32U3B5RI</t>
+          <t>STM32U3B5WI</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>47||51 (workbook and API agree)</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="E82" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>STM32U3B5RI</t>
+          <t>STM32U3B5WI</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>10 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E83" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E83" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>STM32U3B5RI</t>
+          <t>STM32U3B5WI</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E84" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>STM32U3B5RG</t>
+          <t>STM32U3B5WI</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>97</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E85" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>STM32U3B5RG</t>
+          <t>STM32U3B5WI</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>97 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E86" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E86" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>STM32U3B5RG</t>
+          <t>STM32U3B5WI</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>10 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E87" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E87" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>STM32U3B5RG</t>
+          <t>STM32U3B5WI</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>47||51</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="E88" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E88" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>STM32U3B5RG</t>
+          <t>STM32U3C5JI</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>47, 51</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="E89" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E89" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>STM32U3B5RG</t>
+          <t>STM32U3C5JI</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>47||51 (workbook and API agree)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="E90" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>STM32U3B5RG</t>
+          <t>STM32U3C5JI</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E91" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>STM32U3B5RG</t>
+          <t>STM32U3C5JI</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E92" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>STM32U3C5RI</t>
+          <t>STM32U3C5JI</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>97 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E93" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E93" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>STM32U3C5RI</t>
+          <t>STM32U3C5JI</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E94" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E94" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>STM32U3C5RI</t>
+          <t>STM32U3C5JI</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>10 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E95" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E95" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>STM32U3C5RI</t>
+          <t>STM32U3B5QI</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>47||51</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
@@ -2694,22 +2654,22 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>STM32U3C5RI</t>
+          <t>STM32U3B5QI</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>47, 51</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
@@ -2721,22 +2681,22 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>STM32U3C5RI</t>
+          <t>STM32U3B5QI</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>47||51 (workbook and API agree)</t>
+          <t>10 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
@@ -2748,7 +2708,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>STM32U3C5RI</t>
+          <t>STM32U3B5QI</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -2771,7 +2731,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>STM32U3C5RI</t>
+          <t>STM32U3B5QI</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -2794,7 +2754,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>STM32U3B5VI</t>
+          <t>STM32U3B5VG</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -2817,7 +2777,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>STM32U3B5VI</t>
+          <t>STM32U3B5VG</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -2840,68 +2800,76 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>STM32U3C5VI</t>
+          <t>STM32U3B5JI</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E103" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E103" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>STM32U3C5VI</t>
+          <t>STM32U3B5JI</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr"/>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E104" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E104" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>STM32U3B5WI</t>
+          <t>STM32U3B5JI</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>55</t>
         </is>
       </c>
       <c r="E105" s="3" t="inlineStr">
@@ -2913,22 +2881,22 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>STM32U3B5WI</t>
+          <t>STM32U3B5JI</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>55</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
@@ -2940,22 +2908,22 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>STM32U3B5WI</t>
+          <t>STM32U3B5JI</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>10 (workbook and API agree)</t>
+          <t>47 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>55</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
@@ -2967,7 +2935,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>STM32U3B5WI</t>
+          <t>STM32U3B5JI</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -2990,7 +2958,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>STM32U3B5WI</t>
+          <t>STM32U3B5JI</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3013,7 +2981,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>STM32U3C5JI</t>
+          <t>STM32U3B5ZG</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3023,7 +2991,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3031,77 +2999,81 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E110" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+      <c r="E110" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>STM32U3C5JI</t>
+          <t>STM32U3B5ZG</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E111" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E111" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>STM32U3C5JI</t>
+          <t>STM32U3B5ZG</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>10 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E112" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E112" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>STM32U3C5JI</t>
+          <t>STM32U3B5ZG</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E113" s="6" t="inlineStr">
@@ -3113,34 +3085,30 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>STM32U3B5QI</t>
+          <t>STM32U3B5ZG</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E114" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E114" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>STM32U3B5QI</t>
+          <t>STM32U3B5QG</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3158,16 +3126,16 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E115" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E115" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>STM32U3B5QI</t>
+          <t>STM32U3B5QG</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3177,7 +3145,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>10 (workbook and API agree)</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -3185,254 +3153,258 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E116" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E116" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>STM32U3B5QI</t>
+          <t>STM32U3B5QG</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>106||110</t>
+          <t>10 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="E117" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E117" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>STM32U3B5QI</t>
+          <t>STM32U3B5QG</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>106, 110</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr">
         <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="E118" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E118" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>STM32U3B5QI</t>
+          <t>STM32U3B5QG</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>106||110 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr">
         <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="E119" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E119" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>STM32U3B5QI</t>
+          <t>STM32U3B5JG</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E120" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E120" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>STM32U3B5QI</t>
+          <t>STM32U3B5JG</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr"/>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E121" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E121" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>STM32U3B5VG</t>
+          <t>STM32U3B5JG</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E122" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E122" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>STM32U3B5VG</t>
+          <t>STM32U3B5JG</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E123" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E123" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>STM32U3B5JI</t>
+          <t>STM32U3B5JG</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>47 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E124" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E124" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>STM32U3B5JI</t>
+          <t>STM32U3B5JG</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E125" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E125" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>STM32U3B5JI</t>
+          <t>STM32U3B5JG</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E126" s="6" t="inlineStr">
@@ -3441,547 +3413,8 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>STM32U3B5JI</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr"/>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E127" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>STM32U3B5ZG</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E128" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>STM32U3B5ZG</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E129" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>STM32U3B5ZG</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>10 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E130" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>STM32U3B5ZG</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>111||114</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="E131" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>STM32U3B5ZG</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>111, 114</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="E132" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>STM32U3B5ZG</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>111||114 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="E133" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>STM32U3B5ZG</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr"/>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E134" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>STM32U3B5ZG</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr"/>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E135" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>STM32U3B5QG</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E136" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>STM32U3B5QG</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E137" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>STM32U3B5QG</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>10 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E138" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>STM32U3B5QG</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>106||110</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="E139" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>STM32U3B5QG</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>106, 110</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="E140" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>STM32U3B5QG</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>106||110 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="E141" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>STM32U3B5QG</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr"/>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E142" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>STM32U3B5QG</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr"/>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E143" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>STM32U3B5JG</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E144" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>STM32U3B5JG</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E145" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>STM32U3B5JG</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr"/>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E146" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>STM32U3B5JG</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr"/>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E147" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A18:E147"/>
+  <autoFilter ref="A18:E126"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/product_selector_out/STM32U3B5-3C5 - diff.xlsx
+++ b/product_selector_out/STM32U3B5-3C5 - diff.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Diff" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$126</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$144</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E126"/>
+  <dimension ref="A1:E144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -525,7 +525,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1344</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="6">
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1276</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="18">
@@ -795,27 +795,23 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>STM32U3B5CI</t>
+          <t>STM32U3B5CG</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -840,9 +836,9 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -859,7 +855,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>10 (workbook and API agree)</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -867,9 +863,9 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -881,18 +877,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>10 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E27" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -904,13 +904,13 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
@@ -922,54 +922,46 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STM32U3C5CI</t>
+          <t>STM32U3B5CI</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STM32U3C5CI</t>
+          <t>STM32U3B5CI</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -986,7 +978,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>10 (workbook and API agree)</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -994,9 +986,9 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -1008,18 +1000,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E32" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -1031,99 +1027,91 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>10 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E33" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STM32U3B5ZI</t>
+          <t>STM32U3C5CI</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STM32U3B5ZI</t>
+          <t>STM32U3C5CI</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STM32U3B5ZI</t>
+          <t>STM32U3C5CI</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>10 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -1135,18 +1123,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E37" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -1158,25 +1150,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E38" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STM32U3C5ZI</t>
+          <t>STM32U3B5ZI</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1186,7 +1182,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1194,81 +1190,73 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>STM32U3C5ZI</t>
+          <t>STM32U3B5ZI</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>STM32U3C5ZI</t>
+          <t>STM32U3B5ZI</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>10 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E41" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>STM32U3C5ZI</t>
+          <t>STM32U3B5ZI</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
@@ -1285,25 +1273,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E43" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STM32U3C5QI</t>
+          <t>STM32U3C5ZI</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1321,16 +1313,16 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>STM32U3C5QI</t>
+          <t>STM32U3C5ZI</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1340,7 +1332,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1348,54 +1340,50 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>STM32U3C5QI</t>
+          <t>STM32U3C5ZI</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>10 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E46" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>STM32U3C5QI</t>
+          <t>STM32U3C5ZI</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
@@ -1407,18 +1395,18 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>STM32U3C5QI</t>
+          <t>STM32U3C5ZI</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
@@ -1430,7 +1418,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STM32U3B5WG</t>
+          <t>STM32U3C5QI</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1457,7 +1445,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STM32U3B5WG</t>
+          <t>STM32U3C5QI</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1484,7 +1472,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>STM32U3B5WG</t>
+          <t>STM32U3C5QI</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1511,7 +1499,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>STM32U3B5WG</t>
+          <t>STM32U3C5QI</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1534,7 +1522,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>STM32U3B5WG</t>
+          <t>STM32U3C5QI</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1557,34 +1545,30 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>STM32U3C5WI</t>
+          <t>STM32U3C5QI</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E54" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>STM32U3C5WI</t>
+          <t>STM32U3B5WG</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1602,16 +1586,16 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>STM32U3C5WI</t>
+          <t>STM32U3B5WG</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1621,7 +1605,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>10 (workbook and API agree)</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1629,108 +1613,100 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E56" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>STM32U3C5WI</t>
+          <t>STM32U3B5WG</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>10 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="E57" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>STM32U3C5WI</t>
+          <t>STM32U3B5WG</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="E58" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>STM32U3C5WI</t>
+          <t>STM32U3B5WG</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>97 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="E59" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STM32U3C5WI</t>
+          <t>STM32U3B5WG</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
@@ -1747,25 +1723,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E61" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>STM32U3B5RI</t>
+          <t>STM32U3C5WI</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1783,16 +1763,16 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E62" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STM32U3B5RI</t>
+          <t>STM32U3C5WI</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1802,7 +1782,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -1810,216 +1790,220 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>STM32U3B5RI</t>
+          <t>STM32U3C5WI</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>10 (workbook and API agree)</t>
+          <t>97</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E64" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>STM32U3B5RI</t>
+          <t>STM32U3C5WI</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E65" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>STM32U3B5RI</t>
+          <t>STM32U3C5WI</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>97 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E66" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STM32U3B5RG</t>
+          <t>STM32U3C5WI</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E67" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>STM32U3B5RG</t>
+          <t>STM32U3C5WI</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E68" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STM32U3B5RG</t>
+          <t>STM32U3C5WI</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>10 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E69" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>STM32U3B5RG</t>
+          <t>STM32U3B5RI</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E70" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>STM32U3B5RG</t>
+          <t>STM32U3B5RI</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E71" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>STM32U3C5RI</t>
+          <t>STM32U3B5RI</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2029,7 +2013,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2037,81 +2021,73 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E72" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E72" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>STM32U3C5RI</t>
+          <t>STM32U3B5RI</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E73" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>STM32U3C5RI</t>
+          <t>STM32U3B5RI</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>10 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E74" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E74" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>STM32U3C5RI</t>
+          <t>STM32U3B5RI</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
@@ -2123,76 +2099,88 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>STM32U3C5RI</t>
+          <t>STM32U3B5RG</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E76" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>STM32U3B5VI</t>
+          <t>STM32U3B5RG</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E77" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>STM32U3B5VI</t>
+          <t>STM32U3B5RG</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>10 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E78" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>STM32U3C5VI</t>
+          <t>STM32U3B5RG</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2215,7 +2203,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>STM32U3C5VI</t>
+          <t>STM32U3B5RG</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2238,34 +2226,30 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>STM32U3B5WI</t>
+          <t>STM32U3B5RG</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E81" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>STM32U3B5WI</t>
+          <t>STM32U3C5RI</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2283,16 +2267,16 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E82" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>STM32U3B5WI</t>
+          <t>STM32U3C5RI</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2302,7 +2286,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>10 (workbook and API agree)</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2310,108 +2294,100 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E83" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>STM32U3B5WI</t>
+          <t>STM32U3C5RI</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>10 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="E84" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E84" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>STM32U3B5WI</t>
+          <t>STM32U3C5RI</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="E85" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E85" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>STM32U3B5WI</t>
+          <t>STM32U3C5RI</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>97 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="E86" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E86" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>STM32U3B5WI</t>
+          <t>STM32U3C5RI</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
@@ -2423,18 +2399,18 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>STM32U3B5WI</t>
+          <t>STM32U3B5VI</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
@@ -2446,280 +2422,272 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>STM32U3C5JI</t>
+          <t>STM32U3B5VI</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E89" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E89" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>STM32U3C5JI</t>
+          <t>STM32U3C5VI</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E90" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E90" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>STM32U3C5JI</t>
+          <t>STM32U3C5VI</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="E91" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E91" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>STM32U3C5JI</t>
+          <t>STM32U3B5WI</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="E92" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>STM32U3C5JI</t>
+          <t>STM32U3B5WI</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>97 (workbook and API agree)</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="E93" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>STM32U3C5JI</t>
+          <t>STM32U3B5WI</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>10 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E94" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E94" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>STM32U3C5JI</t>
+          <t>STM32U3B5WI</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E95" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>STM32U3B5QI</t>
+          <t>STM32U3B5WI</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>97</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E96" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>STM32U3B5QI</t>
+          <t>STM32U3B5WI</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>97 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E97" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E97" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>STM32U3B5QI</t>
+          <t>STM32U3B5WI</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>10 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E98" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E98" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>STM32U3B5QI</t>
+          <t>STM32U3B5WI</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
@@ -2731,18 +2699,18 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>STM32U3B5QI</t>
+          <t>STM32U3B5WI</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
@@ -2754,107 +2722,115 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>STM32U3B5VG</t>
+          <t>STM32U3C5JI</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E101" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E101" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>STM32U3B5VG</t>
+          <t>STM32U3C5JI</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr"/>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E102" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E102" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>STM32U3B5JI</t>
+          <t>STM32U3C5JI</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E103" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>STM32U3B5JI</t>
+          <t>STM32U3C5JI</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E104" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E104" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>STM32U3B5JI</t>
+          <t>STM32U3C5JI</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2864,7 +2840,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>97 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -2872,81 +2848,73 @@
           <t>55</t>
         </is>
       </c>
-      <c r="E105" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E105" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>STM32U3B5JI</t>
+          <t>STM32U3C5JI</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr">
         <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="E106" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E106" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>STM32U3B5JI</t>
+          <t>STM32U3C5JI</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>47 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr">
         <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="E107" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E107" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>STM32U3B5JI</t>
+          <t>STM32U3C5JI</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
@@ -2958,30 +2926,34 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>STM32U3B5JI</t>
+          <t>STM32U3B5QI</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E109" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>STM32U3B5ZG</t>
+          <t>STM32U3B5QI</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -2999,16 +2971,16 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E110" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E110" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>STM32U3B5ZG</t>
+          <t>STM32U3B5QI</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3018,7 +2990,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -3026,54 +2998,50 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E111" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E111" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>STM32U3B5ZG</t>
+          <t>STM32U3B5QI</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>10 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E112" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E112" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>STM32U3B5ZG</t>
+          <t>STM32U3B5QI</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E113" s="6" t="inlineStr">
@@ -3085,18 +3053,18 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>STM32U3B5ZG</t>
+          <t>STM32U3B5QI</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E114" s="6" t="inlineStr">
@@ -3108,61 +3076,53 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>STM32U3B5QG</t>
+          <t>STM32U3B5VG</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E115" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E115" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>STM32U3B5QG</t>
+          <t>STM32U3B5VG</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E116" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E116" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>STM32U3B5QG</t>
+          <t>STM32U3B5JI</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3172,7 +3132,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>10 (workbook and API agree)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -3180,241 +3140,695 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E117" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E117" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>STM32U3B5QG</t>
+          <t>STM32U3B5JI</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr"/>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E118" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E118" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>STM32U3B5QG</t>
+          <t>STM32U3B5JI</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E119" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E119" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>STM32U3B5JG</t>
+          <t>STM32U3B5JI</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E120" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E120" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>STM32U3B5JG</t>
+          <t>STM32U3B5JI</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>47 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E121" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E121" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>STM32U3B5JG</t>
+          <t>STM32U3B5JI</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr">
         <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="E122" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E122" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>STM32U3B5JG</t>
+          <t>STM32U3B5JI</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr">
         <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="E123" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E123" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>STM32U3B5JG</t>
+          <t>STM32U3B5JI</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>47 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr">
         <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="E124" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E124" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>STM32U3B5JG</t>
+          <t>STM32U3B5ZG</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E125" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E125" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
+          <t>STM32U3B5ZG</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E126" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>STM32U3B5ZG</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>10 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E127" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>STM32U3B5ZG</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E128" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>STM32U3B5ZG</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E129" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>STM32U3B5ZG</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E130" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>STM32U3B5QG</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E131" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>STM32U3B5QG</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E132" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>STM32U3B5QG</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>10 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E133" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>STM32U3B5QG</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E134" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>STM32U3B5QG</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E135" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>STM32U3B5QG</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E136" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
           <t>STM32U3B5JG</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr">
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E137" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>STM32U3B5JG</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E138" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>STM32U3B5JG</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E139" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>STM32U3B5JG</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E140" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>STM32U3B5JG</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>47 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E141" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>STM32U3B5JG</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E142" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>STM32U3B5JG</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
         <is>
           <t>Longevity Starting Date</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr"/>
-      <c r="D126" t="inlineStr">
+      <c r="C143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
         <is>
           <t>2026-03-03T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E126" s="6" t="inlineStr">
+      <c r="E143" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>STM32U3B5JG</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E144" s="6" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A18:E126"/>
+  <autoFilter ref="A18:E144"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>